--- a/data_input/sugc_soil_params_rain_high.xlsx
+++ b/data_input/sugc_soil_params_rain_high.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dario_outputs\PyAEZ\data_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C68F71-3288-49D7-81D8-2A42F87B1F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B972C8D5-17A6-40C0-9DB3-82238CDDFD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="6" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
   </bookViews>
   <sheets>
     <sheet name="SQ1" sheetId="1" r:id="rId1"/>
